--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484722_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484722_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.772</v>
+        <v>8.6873</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1297</v>
+        <v>3.7858</v>
       </c>
       <c r="F2" t="n">
-        <v>5.6423</v>
+        <v>4.9016</v>
       </c>
       <c r="G2" t="n">
         <v>4.0983</v>
@@ -610,13 +610,13 @@
         <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5982</v>
+        <v>2.5135</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6846</v>
+        <v>1.3407</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9136</v>
+        <v>1.1729</v>
       </c>
       <c r="V2" t="n">
         <v>1.8868</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1191</v>
+        <v>6.1187</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8646</v>
+        <v>5.9435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2545</v>
+        <v>0.1752</v>
       </c>
       <c r="G3" t="n">
         <v>5.6894</v>
@@ -688,13 +688,13 @@
         <v>0.9435</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.618</v>
       </c>
       <c r="T3" t="n">
-        <v>0.77</v>
+        <v>0.849</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1516</v>
+        <v>-0.231</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.289</v>
+        <v>3.5221</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5498</v>
+        <v>3.8622</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2608</v>
+        <v>-0.3401</v>
       </c>
       <c r="G4" t="n">
         <v>1.371</v>
@@ -766,13 +766,13 @@
         <v>1.1322</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1822</v>
+        <v>0.4153</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2039</v>
+        <v>0.5164</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0217</v>
+        <v>-0.1011</v>
       </c>
       <c r="V4" t="n">
         <v>0.6036</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2558</v>
+        <v>3.1705</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1995</v>
+        <v>0.6372</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0564</v>
+        <v>2.5333</v>
       </c>
       <c r="G5" t="n">
-        <v>0.119</v>
+        <v>1.9091</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4594</v>
+        <v>0.1581</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5783</v>
+        <v>1.751</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2666</v>
+        <v>1.267</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1432</v>
+        <v>0.5337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1234</v>
+        <v>0.7333</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1476</v>
+        <v>0.6421</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6026</v>
+        <v>-0.3756</v>
       </c>
       <c r="O5" t="n">
-        <v>0.455</v>
+        <v>1.0177</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1322</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9435</v>
+        <v>1.3209</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8542</v>
+        <v>0.884</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5937</v>
+        <v>0.3137</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2605</v>
+        <v>0.5703</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4714</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4714</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.644</v>
+        <v>3.1109</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5076</v>
+        <v>2.2398</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1364</v>
+        <v>0.8712</v>
       </c>
       <c r="G6" t="n">
-        <v>3.032</v>
+        <v>0.119</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5879</v>
+        <v>-0.4594</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4441</v>
+        <v>0.5783</v>
       </c>
       <c r="J6" t="n">
-        <v>2.357</v>
+        <v>0.2666</v>
       </c>
       <c r="K6" t="n">
-        <v>1.411</v>
+        <v>0.1432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.946</v>
+        <v>0.1234</v>
       </c>
       <c r="M6" t="n">
-        <v>0.675</v>
+        <v>-0.1476</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1769</v>
+        <v>-0.6026</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4981</v>
+        <v>0.455</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3209</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8305</v>
+        <v>-1.1322</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9329</v>
+        <v>0.7093</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7359</v>
+        <v>0.634</v>
       </c>
       <c r="U6" t="n">
-        <v>0.197</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.4714</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2452</v>
+        <v>2.4714</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0438</v>
+        <v>2.8757</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3573</v>
+        <v>1.5277</v>
       </c>
       <c r="F7" t="n">
-        <v>2.401</v>
+        <v>1.348</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9091</v>
+        <v>3.032</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1581</v>
+        <v>1.5879</v>
       </c>
       <c r="I7" t="n">
-        <v>1.751</v>
+        <v>1.4441</v>
       </c>
       <c r="J7" t="n">
-        <v>1.267</v>
+        <v>2.357</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5337</v>
+        <v>1.411</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7333</v>
+        <v>0.946</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6421</v>
+        <v>0.675</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3756</v>
+        <v>0.1769</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0177</v>
+        <v>0.4981</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3774</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2428</v>
+        <v>1.1647</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6808</v>
+        <v>0.7561</v>
       </c>
       <c r="U7" t="n">
-        <v>0.438</v>
+        <v>0.4086</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1734</v>
+        <v>2.075</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1734</v>
+        <v>1.8369</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.2381</v>
       </c>
       <c r="G8" t="n">
         <v>0.8557</v>
@@ -1078,13 +1078,13 @@
         <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0787</v>
+        <v>-0.1771</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5879</v>
+        <v>0.0757</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4908</v>
+        <v>-0.2527</v>
       </c>
       <c r="V8" t="n">
         <v>0.6415999999999999</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9552</v>
+        <v>0.6302</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9485</v>
+        <v>-1.2206</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9037</v>
+        <v>1.8508</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5019</v>
@@ -1156,13 +1156,13 @@
         <v>1.887</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7588</v>
+        <v>1.4338</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1503</v>
+        <v>0.8782</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6085</v>
+        <v>0.5556</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5023</v>
+        <v>-0.1429</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.6864</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4377</v>
+        <v>0.5435</v>
       </c>
       <c r="G10" t="n">
         <v>0.6304</v>
@@ -1234,13 +1234,13 @@
         <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.378</v>
+        <v>-0.0185</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0588</v>
+        <v>0.1949</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3192</v>
+        <v>-0.2134</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4997</v>
+        <v>-3.3277</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.739</v>
+        <v>-5.0167</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2393</v>
+        <v>1.689</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2658</v>
@@ -1312,13 +1312,13 @@
         <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3468</v>
+        <v>0.8252</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1735</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1734</v>
+        <v>0.2763</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3018</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>25.25030000000001</v>
+        <v>26.7198</v>
       </c>
       <c r="E12" t="n">
-        <v>11.4398</v>
+        <v>12.9094</v>
       </c>
       <c r="F12" t="n">
-        <v>13.8105</v>
+        <v>13.8106</v>
       </c>
       <c r="G12" t="n">
         <v>14.9372</v>
@@ -1360,7 +1360,7 @@
         <v>5.1965</v>
       </c>
       <c r="I12" t="n">
-        <v>9.7407</v>
+        <v>9.740699999999999</v>
       </c>
       <c r="J12" t="n">
         <v>13.8424</v>
@@ -1390,19 +1390,19 @@
         <v>12.2655</v>
       </c>
       <c r="S12" t="n">
-        <v>6.8984</v>
+        <v>8.3682</v>
       </c>
       <c r="T12" t="n">
-        <v>4.6374</v>
+        <v>6.107599999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2609</v>
+        <v>2.2608</v>
       </c>
       <c r="V12" t="n">
         <v>5.301600000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>7.112399999999999</v>
+        <v>7.1124</v>
       </c>
       <c r="X12" t="n">
         <v>-1.8108</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9901</v>
+        <v>2.3209</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4868</v>
+        <v>4.5842</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4967</v>
+        <v>-2.2633</v>
       </c>
       <c r="G13" t="n">
         <v>1.1566</v>
@@ -1468,13 +1468,13 @@
         <v>2.4531</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2797</v>
+        <v>-0.9489</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4892</v>
+        <v>-0.3917</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7906</v>
+        <v>-0.5572</v>
       </c>
       <c r="V13" t="n">
         <v>0.6036</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1996</v>
+        <v>0.297</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0335</v>
+        <v>0.1309</v>
       </c>
       <c r="F14" t="n">
         <v>0.1661</v>
@@ -1546,10 +1546,10 @@
         <v>0.3774</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2475</v>
+        <v>-0.1501</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0123</v>
+        <v>0.1098</v>
       </c>
       <c r="U14" t="n">
         <v>-0.2598</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. DURAN OLMOS</t>
+          <t>N. ALBALADEJO PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7489</v>
+        <v>-0.5785</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8084</v>
+        <v>-1.0904</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5573</v>
+        <v>0.5119</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1451</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4007</v>
+        <v>2.0128</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5457</v>
+        <v>-2.6323</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9007</v>
+        <v>0.4953</v>
       </c>
       <c r="K15" t="n">
-        <v>0.576</v>
+        <v>1.1363</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3247</v>
+        <v>-0.641</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7556</v>
+        <v>-1.1148</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9767</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7789</v>
+        <v>-1.9913</v>
       </c>
       <c r="P15" t="n">
         <v>0.5661</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5096</v>
+        <v>1.6983</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8565</v>
+        <v>-0.5251</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1488</v>
+        <v>-0.4534</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7077</v>
+        <v>-0.0717</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. ALBALADEJO PEREZ</t>
+          <t>I. DURAN OLMOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8611</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1878</v>
+        <v>0.7109</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3267</v>
+        <v>-1.4827</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6195000000000001</v>
+        <v>0.1451</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0128</v>
+        <v>-0.4007</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.6323</v>
+        <v>0.5457</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4953</v>
+        <v>1.9007</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1363</v>
+        <v>0.576</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.641</v>
+        <v>1.3247</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1148</v>
+        <v>-1.7556</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8764999999999999</v>
+        <v>-0.9767</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9913</v>
+        <v>-0.7789</v>
       </c>
       <c r="P16" t="n">
         <v>0.5661</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1322</v>
+        <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6983</v>
+        <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8077</v>
+        <v>-0.8793</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.2462</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2568</v>
+        <v>-0.633</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. RUIZ FRANCO</t>
+          <t>C. SEVERA LENCINA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.69</v>
+        <v>-2.5672</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0222</v>
+        <v>-2.2473</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.32</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7442</v>
+        <v>-1.3797</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6339</v>
+        <v>-1.0291</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1103</v>
+        <v>-0.3506</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0411</v>
+        <v>-1.0267</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-0.4594</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0411</v>
+        <v>-0.5673</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7854</v>
+        <v>-0.353</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6339</v>
+        <v>-0.5697</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1515</v>
+        <v>0.2167</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5096</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.887</v>
+        <v>-1.1322</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4362</v>
+        <v>-0.2065</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1764</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2598</v>
+        <v>-0.1181</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. SEVERA LENCINA</t>
+          <t>D. RUIZ FRANCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1337</v>
+        <v>-2.69</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.7344</v>
+        <v>-2.0222</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3993</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3797</v>
+        <v>-0.7442</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0291</v>
+        <v>-0.6339</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3506</v>
+        <v>-0.1103</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0267</v>
+        <v>0.0411</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4594</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5673</v>
+        <v>0.0411</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.353</v>
+        <v>-0.7854</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5697</v>
+        <v>-0.6339</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2167</v>
+        <v>-0.1515</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3774</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.773</v>
+        <v>-0.4362</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5755</v>
+        <v>-0.1764</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1975</v>
+        <v>-0.2598</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6789</v>
+        <v>-3.1087</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8553</v>
+        <v>-1.4656</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8235</v>
+        <v>-1.643</v>
       </c>
       <c r="G19" t="n">
         <v>0.3501</v>
@@ -1936,13 +1936,13 @@
         <v>2.0757</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8593</v>
+        <v>-1.2891</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2687</v>
+        <v>-0.8789</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5907</v>
+        <v>-0.4102</v>
       </c>
       <c r="V19" t="n">
         <v>-2.1696</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.6071</v>
+        <v>-5.6933</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4651</v>
+        <v>-3.7317</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.142</v>
+        <v>-1.9616</v>
       </c>
       <c r="G20" t="n">
         <v>-6.008</v>
@@ -2014,13 +2014,13 @@
         <v>2.8305</v>
       </c>
       <c r="S20" t="n">
-        <v>0.646</v>
+        <v>-0.4402</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2367</v>
+        <v>-0.03</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5907</v>
+        <v>-0.4102</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9434</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-11.7202</v>
+        <v>-11.1597</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.8742</v>
+        <v>-8.679399999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8459</v>
+        <v>-2.4803</v>
       </c>
       <c r="G21" t="n">
         <v>-7.9072</v>
@@ -2092,13 +2092,13 @@
         <v>2.0757</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2845</v>
+        <v>-0.724</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3005</v>
+        <v>-0.1056</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.984</v>
+        <v>-0.6183</v>
       </c>
       <c r="V21" t="n">
         <v>-1.585</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-25.2502</v>
+        <v>-23.9512</v>
       </c>
       <c r="E22" t="n">
-        <v>-13.8103</v>
+        <v>-13.8106</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.4397</v>
+        <v>-10.1407</v>
       </c>
       <c r="G22" t="n">
         <v>-14.9371</v>
@@ -2170,13 +2170,13 @@
         <v>14.1525</v>
       </c>
       <c r="S22" t="n">
-        <v>-6.898400000000001</v>
+        <v>-5.5994</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.261</v>
+        <v>-2.2608</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.6376</v>
+        <v>-3.3383</v>
       </c>
       <c r="V22" t="n">
         <v>-5.301600000000001</v>
